--- a/artfynd/A 55700-2025 artfynd.xlsx
+++ b/artfynd/A 55700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,68 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6333202</v>
+        <v>119102244</v>
       </c>
       <c r="B2" t="n">
-        <v>103652</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>225197</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Äkta ljungsnärja</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cuscuta epithymum var. epithymum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bokvarn, 850 m NV, hagmark, Hallonstugans grund, Srm</t>
+          <t>Hallonstugan, svinrot vid vägen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562436.7409790338</v>
+        <v>562331</v>
       </c>
       <c r="R2" t="n">
-        <v>6537538.468263197</v>
+        <v>6537611</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -742,29 +758,24 @@
           <t>Östra Vingåker</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>D-Kat-0629</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1995-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hagmark kring f.d. Hallonstugan</t>
+          <t>i vägdiket</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,31 +784,426 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Artificiell miljö</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>betesmark</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
+          <t>vägslänter</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>119102216</v>
+      </c>
+      <c r="B3" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hallonstugan, gullklöver  vid vägen, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>562364</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6537591</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Östra Vingåker</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D-Kat-0630</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 dellokaler</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Artificiell miljö</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vägslänter</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>87523417</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hallonstugan backklöver 50 m so, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>562424</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6537538</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Östra Vingåker</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D-Kat-0544</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-08-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-08-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>vägslänt</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6333202</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106650</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>225197</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Äkta ljungsnärja</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cuscuta epithymum var. epithymum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bokvarn, 850 m NV, hagmark, Hallonstugans grund, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>562437</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6537538</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Östra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1995-08-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1995-08-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hagmark kring f.d. Hallonstugan</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>betesmark</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Lennart Karlén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Lennart Karlén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55700-2025 artfynd.xlsx
+++ b/artfynd/A 55700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -814,6 +819,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119102244</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -956,6 +966,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119102216</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1091,6 +1106,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87523417</t>
         </is>
       </c>
     </row>
@@ -1204,8 +1224,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6333202</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>